--- a/experiment/Omni+CNN_2CH_bestx4/Test/results-B100/B100.xlsx
+++ b/experiment/Omni+CNN_2CH_bestx4/Test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.09</v>
+        <v>24.07</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5746</v>
+        <v>0.5749</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.75</v>
+        <v>28.76</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8145</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.59</v>
+        <v>26.58</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8145</v>
+        <v>0.8156</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.65</v>
+        <v>30.64</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8492</v>
+        <v>0.8489</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>26.27</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7113</v>
+        <v>0.7119</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.97</v>
+        <v>34.03</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8937</v>
+        <v>0.8935</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.32</v>
+        <v>26.33</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7527</v>
+        <v>0.7524999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.13</v>
+        <v>23.1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5938</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="10">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.47</v>
+        <v>27.48</v>
       </c>
       <c r="C10" t="n">
         <v>0.7886</v>
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.36</v>
+        <v>29.37</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8045</v>
+        <v>0.8048999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.66</v>
+        <v>24.64</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7407</v>
+        <v>0.7403999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.03</v>
+        <v>28.1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7548</v>
+        <v>0.7566000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.04</v>
+        <v>30.03</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8086</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.47</v>
+        <v>29.54</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8328</v>
+        <v>0.8342000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.07</v>
+        <v>25.06</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6797</v>
+        <v>0.6802</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7613</v>
+        <v>0.7603</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.75</v>
+        <v>34.78</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8927</v>
+        <v>0.8932</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33.03</v>
+        <v>32.98</v>
       </c>
       <c r="C19" t="n">
-        <v>0.895</v>
+        <v>0.8944</v>
       </c>
     </row>
     <row r="20">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26.23</v>
+        <v>26.22</v>
       </c>
       <c r="C20" t="n">
         <v>0.7398</v>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26.03</v>
+        <v>26.02</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8014</v>
+        <v>0.8008999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.27</v>
+        <v>22.21</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6963</v>
+        <v>0.6944</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.91</v>
+        <v>23.92</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6331</v>
+        <v>0.6342</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         <v>24.84</v>
       </c>
       <c r="C24" t="n">
-        <v>0.573</v>
+        <v>0.5735</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.63</v>
+        <v>26.64</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7968</v>
+        <v>0.7965</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27.7</v>
+        <v>27.69</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8235</v>
+        <v>0.8237</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.02</v>
+        <v>26.98</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8403</v>
+        <v>0.8396</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.8</v>
+        <v>27.81</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7383</v>
+        <v>0.7393999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.58</v>
+        <v>29.62</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8031</v>
+        <v>0.8038999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.6</v>
+        <v>32.63</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9013</v>
+        <v>0.9018</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.92</v>
+        <v>19.9</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5072</v>
+        <v>0.5082</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +845,7 @@
         <v>29.81</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8183</v>
+        <v>0.8181</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.93</v>
+        <v>20.92</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4313</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.21</v>
+        <v>25.19</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6747</v>
+        <v>0.6738</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.6</v>
+        <v>24.56</v>
       </c>
       <c r="C35" t="n">
-        <v>0.762</v>
+        <v>0.7616000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35</v>
+        <v>35.07</v>
       </c>
       <c r="C36" t="n">
         <v>0.8937</v>
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27.02</v>
+        <v>27.04</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7443</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         <v>27.94</v>
       </c>
       <c r="C38" t="n">
-        <v>0.514</v>
+        <v>0.5138</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         <v>28.27</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7184</v>
+        <v>0.7183</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.56</v>
+        <v>28.54</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7476</v>
+        <v>0.7484</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36.22</v>
+        <v>36.25</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9583</v>
+        <v>0.9582000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.93</v>
+        <v>27.01</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7486</v>
+        <v>0.7493</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.9</v>
+        <v>25.91</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7261</v>
+        <v>0.7256</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.77</v>
+        <v>26.8</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7622</v>
+        <v>0.7627</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         <v>28.12</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8777</v>
+        <v>0.8779</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.83</v>
+        <v>24.85</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6849</v>
+        <v>0.6866</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.77</v>
+        <v>34.76</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8734</v>
+        <v>0.8728</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.81</v>
+        <v>22.79</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6259</v>
+        <v>0.6257</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25</v>
+        <v>25.01</v>
       </c>
       <c r="C49" t="n">
-        <v>0.636</v>
+        <v>0.6363</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.3</v>
+        <v>27.39</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8768</v>
+        <v>0.8791</v>
       </c>
     </row>
     <row r="51">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.22</v>
+        <v>32.2</v>
       </c>
       <c r="C51" t="n">
         <v>0.8408</v>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.88</v>
+        <v>24.85</v>
       </c>
       <c r="C52" t="n">
-        <v>0.621</v>
+        <v>0.6206</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.52</v>
+        <v>22.57</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7062</v>
+        <v>0.7092000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.52</v>
+        <v>32.43</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8458</v>
+        <v>0.8444</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.57</v>
+        <v>32.49</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8008</v>
+        <v>0.7989000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.84</v>
+        <v>27.88</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7808</v>
+        <v>0.7821</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.66</v>
+        <v>25.65</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6959</v>
+        <v>0.6972</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>21.48</v>
+        <v>21.47</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4305</v>
+        <v>0.4306</v>
       </c>
     </row>
     <row r="59">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27.51</v>
+        <v>27.53</v>
       </c>
       <c r="C59" t="n">
         <v>0.7292</v>
@@ -1209,7 +1209,7 @@
         <v>32.05</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7932</v>
+        <v>0.7931</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.3</v>
+        <v>31.31</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7862</v>
+        <v>0.7868000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.79</v>
+        <v>31.76</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8162</v>
+        <v>0.8159</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>28.96</v>
+        <v>28.93</v>
       </c>
       <c r="C63" t="n">
-        <v>0.792</v>
+        <v>0.7923</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33.73</v>
+        <v>33.67</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9526</v>
+        <v>0.9529</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         <v>24.35</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6743</v>
+        <v>0.6737</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>26.04</v>
+        <v>26.02</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6214</v>
+        <v>0.6212</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.4</v>
+        <v>28.38</v>
       </c>
       <c r="C67" t="n">
-        <v>0.795</v>
+        <v>0.7949000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>39.87</v>
+        <v>39.82</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9808</v>
+        <v>0.9805</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.07</v>
+        <v>21.04</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5836</v>
+        <v>0.5827</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1339,7 @@
         <v>22.78</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6516</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>29.04</v>
+        <v>28.94</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8132</v>
+        <v>0.8118</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.6</v>
+        <v>30.66</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8202</v>
+        <v>0.8219</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25.48</v>
+        <v>25.49</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5974</v>
+        <v>0.5985</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         <v>27.21</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.6056</v>
       </c>
     </row>
     <row r="75">
@@ -1404,7 +1404,7 @@
         <v>26.3</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6967</v>
+        <v>0.6964</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>24.13</v>
+        <v>24.18</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6995</v>
+        <v>0.7010999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.7</v>
+        <v>30.68</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7852</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         <v>23.66</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4793</v>
+        <v>0.4801</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>29.86</v>
+        <v>29.83</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8121</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.76</v>
+        <v>32.79</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9525</v>
+        <v>0.9522</v>
       </c>
     </row>
     <row r="81">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.78</v>
+        <v>29.79</v>
       </c>
       <c r="C81" t="n">
         <v>0.8198</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.82</v>
+        <v>35.79</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9389</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.53</v>
+        <v>28.52</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7192</v>
+        <v>0.7191</v>
       </c>
     </row>
     <row r="84">
@@ -1521,7 +1521,7 @@
         <v>22.26</v>
       </c>
       <c r="C84" t="n">
-        <v>0.533</v>
+        <v>0.5336</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>21.05</v>
+        <v>21.03</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6091</v>
+        <v>0.6099</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1547,7 @@
         <v>25.61</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7909</v>
+        <v>0.7911</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25.03</v>
+        <v>25.02</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6032</v>
+        <v>0.6051</v>
       </c>
     </row>
     <row r="88">
@@ -1573,7 +1573,7 @@
         <v>27.39</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6964</v>
+        <v>0.6962</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30.72</v>
+        <v>30.73</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8146</v>
+        <v>0.8154</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1599,7 @@
         <v>27.25</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5605</v>
+        <v>0.5614</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.11</v>
+        <v>25.13</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6475</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>29.12</v>
+        <v>29.1</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7156</v>
+        <v>0.7151999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.97</v>
+        <v>30.9</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26</v>
+        <v>25.96</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7169</v>
+        <v>0.7161999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.44</v>
+        <v>26.54</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8118</v>
+        <v>0.8147</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>21.93</v>
+        <v>21.94</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3182</v>
+        <v>0.3228</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>27.03</v>
+        <v>27.02</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5616</v>
+        <v>0.5617</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26.32</v>
+        <v>26.3</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7795</v>
+        <v>0.7798</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.91</v>
+        <v>26.89</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7356</v>
+        <v>0.7362</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.13</v>
+        <v>25.14</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7306</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="102">
@@ -1755,7 +1755,7 @@
         <v>27.59</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7379</v>
+        <v>0.7382</v>
       </c>
     </row>
   </sheetData>
